--- a/StructureDefinition-pharmac-charge-item-definition-special-authority.xlsx
+++ b/StructureDefinition-pharmac-charge-item-definition-special-authority.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-pharmac-charge-item-definition-special-authority.xlsx
+++ b/StructureDefinition-pharmac-charge-item-definition-special-authority.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$92</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3277" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3349" uniqueCount="512">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -691,6 +691,38 @@
   </si>
   <si>
     <t>Base64-encoded JSON Schema (application/schema+json) that defines the structure and validation rules for this Special Authority application form. Clients should base64-decode the value and use the resulting JSON Schema for form rendering and input validation.</t>
+  </si>
+  <si>
+    <t>ChargeItemDefinition.extension:fundingSubsidyAmount</t>
+  </si>
+  <si>
+    <t>fundingSubsidyAmount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir-ig.digital.health.nz/pharmac-schedules/StructureDefinition/funding-subsidy-amount}
+</t>
+  </si>
+  <si>
+    <t>Structured subsidy details</t>
+  </si>
+  <si>
+    <t>Structured subsidy metadata including subsidy type, status, optional amount, and display label.</t>
+  </si>
+  <si>
+    <t>ChargeItemDefinition.extension:scheduleFundingAttributes</t>
+  </si>
+  <si>
+    <t>scheduleFundingAttributes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir-ig.digital.health.nz/pharmac-schedules/StructureDefinition/schedule-funding-attributes}
+</t>
+  </si>
+  <si>
+    <t>Grouped schedule funding attributes</t>
+  </si>
+  <si>
+    <t>Grouped funding attributes including contract markers, dispensing flags, and co-payment markers.</t>
   </si>
   <si>
     <t>ChargeItemDefinition.extension:PricingSection29</t>
@@ -1908,12 +1940,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN90"/>
+  <dimension ref="A1:AN92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="58.1171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="58.1171875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.82421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.05078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1921,7 +1953,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="87.765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="88.32421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -5035,43 +5067,41 @@
         <v>230</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="D28" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N28" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="O28" t="s" s="2">
-        <v>235</v>
-      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -5119,7 +5149,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>236</v>
+        <v>137</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5128,13 +5158,13 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>138</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
@@ -5146,35 +5176,37 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>101</v>
+        <v>237</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>238</v>
@@ -5182,12 +5214,8 @@
       <c r="M29" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>241</v>
-      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5235,28 +5263,28 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
@@ -5264,14 +5292,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5284,25 +5312,25 @@
         <v>21</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5351,7 +5379,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5363,27 +5391,27 @@
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>251</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5391,7 +5419,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>87</v>
@@ -5406,18 +5434,20 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>253</v>
+        <v>101</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5465,10 +5495,10 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>87</v>
@@ -5483,21 +5513,21 @@
         <v>85</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5508,10 +5538,10 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
@@ -5520,18 +5550,20 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5579,13 +5611,13 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
@@ -5597,21 +5629,21 @@
         <v>85</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>21</v>
+        <v>253</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>21</v>
+        <v>261</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5622,10 +5654,10 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
@@ -5634,15 +5666,17 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>101</v>
+        <v>263</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5691,13 +5725,13 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
@@ -5709,35 +5743,35 @@
         <v>85</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>21</v>
+        <v>267</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>21</v>
+        <v>268</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>268</v>
+        <v>21</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
@@ -5746,7 +5780,7 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>270</v>
@@ -5754,7 +5788,9 @@
       <c r="M34" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N34" s="2"/>
+      <c r="N34" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5803,13 +5839,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -5821,7 +5857,7 @@
         <v>85</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
@@ -5832,14 +5868,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5858,13 +5894,13 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>269</v>
+        <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5915,7 +5951,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5942,45 +5978,43 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>21</v>
+        <v>278</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>107</v>
+        <v>279</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -6005,13 +6039,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>280</v>
+        <v>21</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>281</v>
+        <v>21</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>282</v>
+        <v>21</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -6029,13 +6063,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -6047,10 +6081,10 @@
         <v>85</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>283</v>
+        <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>284</v>
+        <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>21</v>
@@ -6058,21 +6092,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>21</v>
@@ -6084,20 +6118,16 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -6145,13 +6175,13 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
@@ -6163,53 +6193,53 @@
         <v>85</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>293</v>
+        <v>21</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>294</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6235,13 +6265,13 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>21</v>
+        <v>291</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6259,10 +6289,10 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>87</v>
@@ -6277,21 +6307,21 @@
         <v>85</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6305,7 +6335,7 @@
         <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6314,19 +6344,19 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>253</v>
+        <v>296</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6375,7 +6405,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6393,35 +6423,35 @@
         <v>85</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>21</v>
+        <v>303</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -6430,16 +6460,16 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6489,13 +6519,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6507,10 +6537,10 @@
         <v>85</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>21</v>
+        <v>309</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6518,10 +6548,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6544,18 +6574,20 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O41" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L41" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6603,7 +6635,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6621,21 +6653,21 @@
         <v>85</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>21</v>
+        <v>316</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6649,7 +6681,7 @@
         <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
@@ -6658,20 +6690,18 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>324</v>
-      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6719,7 +6749,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6737,7 +6767,7 @@
         <v>85</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6746,12 +6776,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6762,10 +6792,10 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6774,16 +6804,16 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6809,13 +6839,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>332</v>
+        <v>21</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>333</v>
+        <v>21</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -6833,13 +6863,13 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
@@ -6851,7 +6881,7 @@
         <v>85</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
@@ -6862,21 +6892,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -6885,20 +6915,22 @@
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6947,13 +6979,13 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -6965,21 +6997,21 @@
         <v>85</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>251</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6990,7 +7022,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6999,19 +7031,19 @@
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7037,13 +7069,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>21</v>
+        <v>341</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -7061,13 +7093,13 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
@@ -7079,25 +7111,25 @@
         <v>85</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>251</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7116,19 +7148,17 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7177,7 +7207,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7195,21 +7225,21 @@
         <v>85</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7229,23 +7259,21 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>358</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7293,7 +7321,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7311,21 +7339,21 @@
         <v>85</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7333,31 +7361,35 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7381,13 +7413,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>363</v>
+        <v>21</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>365</v>
+        <v>21</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7405,7 +7437,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7423,21 +7455,21 @@
         <v>85</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>21</v>
+        <v>362</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>21</v>
+        <v>261</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7457,19 +7489,23 @@
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>253</v>
+        <v>364</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7517,7 +7553,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7529,60 +7565,58 @@
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="B50" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>132</v>
+        <v>337</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>234</v>
-      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7607,46 +7641,46 @@
         <v>21</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>21</v>
+        <v>373</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
@@ -7658,7 +7692,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>376</v>
       </c>
@@ -7671,35 +7705,31 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G51" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G51" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="H51" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>381</v>
-      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -7747,22 +7777,22 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
@@ -7776,21 +7806,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7802,15 +7832,17 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>253</v>
+        <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -7847,34 +7879,34 @@
         <v>21</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
@@ -7886,46 +7918,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>132</v>
+        <v>387</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -7961,19 +7995,19 @@
         <v>21</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7985,10 +8019,10 @@
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
@@ -8000,12 +8034,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8013,35 +8047,31 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>101</v>
+        <v>263</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8089,7 +8119,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8101,10 +8131,10 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
@@ -8118,21 +8148,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -8141,19 +8171,19 @@
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>253</v>
+        <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>396</v>
+        <v>244</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8191,34 +8221,34 @@
         <v>21</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>21</v>
@@ -8232,10 +8262,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8258,17 +8288,19 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O56" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8317,7 +8349,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8332,7 +8364,7 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
@@ -8346,10 +8378,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8372,18 +8404,18 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>408</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8431,7 +8463,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8446,7 +8478,7 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>21</v>
@@ -8458,12 +8490,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8471,13 +8503,13 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>21</v>
@@ -8486,19 +8518,17 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>286</v>
+        <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8547,7 +8577,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8562,7 +8592,7 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>21</v>
@@ -8574,12 +8604,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8587,13 +8617,13 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>21</v>
@@ -8602,19 +8632,17 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8663,7 +8691,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8678,7 +8706,7 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>21</v>
@@ -8690,12 +8718,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8703,33 +8731,35 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G60" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G60" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="H60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K60" t="s" s="2">
-        <v>426</v>
+        <v>296</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8777,13 +8807,13 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
@@ -8792,7 +8822,7 @@
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>85</v>
+        <v>427</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>21</v>
@@ -8806,10 +8836,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8817,10 +8847,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>88</v>
@@ -8829,21 +8859,23 @@
         <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -8891,13 +8923,13 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
@@ -8906,7 +8938,7 @@
         <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>85</v>
+        <v>434</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>21</v>
@@ -8918,7 +8950,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>435</v>
       </c>
@@ -8931,13 +8963,13 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>21</v>
@@ -8946,15 +8978,17 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>253</v>
+        <v>436</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>367</v>
+        <v>437</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9003,22 +9037,22 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>369</v>
+        <v>435</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>21</v>
@@ -9030,16 +9064,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9049,7 +9083,7 @@
         <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>21</v>
@@ -9058,16 +9092,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>132</v>
+        <v>441</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>372</v>
+        <v>442</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>373</v>
+        <v>443</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>234</v>
+        <v>444</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9117,7 +9151,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>375</v>
+        <v>440</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9129,10 +9163,10 @@
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
@@ -9146,46 +9180,42 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>132</v>
+        <v>263</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>439</v>
+        <v>377</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9233,22 +9263,22 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>441</v>
+        <v>379</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>85</v>
+        <v>380</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>21</v>
@@ -9262,21 +9292,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9288,15 +9318,17 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>253</v>
+        <v>132</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>443</v>
+        <v>382</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9345,22 +9377,22 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>442</v>
+        <v>385</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>85</v>
+        <v>380</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
@@ -9374,42 +9406,46 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>253</v>
+        <v>132</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9457,19 +9493,19 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>85</v>
@@ -9486,10 +9522,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9497,7 +9533,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>87</v>
@@ -9512,17 +9548,15 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9571,7 +9605,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9598,12 +9632,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9614,10 +9648,10 @@
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>21</v>
@@ -9626,13 +9660,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>431</v>
+        <v>263</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9683,13 +9717,13 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
@@ -9712,10 +9746,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9738,15 +9772,17 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>367</v>
+        <v>459</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -9795,7 +9831,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>369</v>
+        <v>458</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9807,10 +9843,10 @@
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>21</v>
@@ -9822,16 +9858,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9841,7 +9877,7 @@
         <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>21</v>
@@ -9850,17 +9886,15 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>132</v>
+        <v>441</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>372</v>
+        <v>463</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -9909,7 +9943,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>375</v>
+        <v>462</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9921,10 +9955,10 @@
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>21</v>
@@ -9938,46 +9972,42 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>132</v>
+        <v>263</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>439</v>
+        <v>377</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -10025,22 +10055,22 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>441</v>
+        <v>379</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>85</v>
+        <v>380</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>21</v>
@@ -10054,14 +10084,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10080,16 +10110,16 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>431</v>
+        <v>132</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>459</v>
+        <v>382</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>460</v>
+        <v>383</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>434</v>
+        <v>244</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10139,7 +10169,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>458</v>
+        <v>385</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10151,10 +10181,10 @@
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>85</v>
+        <v>380</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>21</v>
@@ -10168,42 +10198,46 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>253</v>
+        <v>132</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>367</v>
+        <v>449</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
       </c>
@@ -10251,22 +10285,22 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>369</v>
+        <v>451</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>21</v>
@@ -10280,14 +10314,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10306,16 +10340,16 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>132</v>
+        <v>441</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>372</v>
+        <v>469</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>373</v>
+        <v>470</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>234</v>
+        <v>444</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10365,7 +10399,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>375</v>
+        <v>468</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10377,10 +10411,10 @@
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>21</v>
@@ -10394,46 +10428,42 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>132</v>
+        <v>263</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>439</v>
+        <v>377</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
       </c>
@@ -10481,22 +10511,22 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>441</v>
+        <v>379</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>85</v>
+        <v>380</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>21</v>
@@ -10510,21 +10540,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
@@ -10536,15 +10566,17 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>253</v>
+        <v>132</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>465</v>
+        <v>382</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -10593,22 +10625,22 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>442</v>
+        <v>385</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>85</v>
+        <v>380</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>21</v>
@@ -10622,42 +10654,46 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>253</v>
+        <v>132</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -10705,19 +10741,19 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>85</v>
@@ -10734,10 +10770,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10745,7 +10781,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>87</v>
@@ -10760,17 +10796,15 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -10819,7 +10853,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10846,12 +10880,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10862,10 +10896,10 @@
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>21</v>
@@ -10874,13 +10908,13 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>431</v>
+        <v>263</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10931,13 +10965,13 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>21</v>
@@ -10960,10 +10994,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10986,15 +11020,17 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>367</v>
+        <v>481</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -11043,7 +11079,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>369</v>
+        <v>458</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11055,10 +11091,10 @@
         <v>21</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>21</v>
@@ -11070,16 +11106,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11089,7 +11125,7 @@
         <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>21</v>
@@ -11098,17 +11134,15 @@
         <v>21</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>132</v>
+        <v>441</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>372</v>
+        <v>484</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -11157,7 +11191,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>375</v>
+        <v>483</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11169,10 +11203,10 @@
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>21</v>
@@ -11186,46 +11220,42 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>132</v>
+        <v>263</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>439</v>
+        <v>377</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>21</v>
       </c>
@@ -11273,22 +11303,22 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>441</v>
+        <v>379</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>85</v>
+        <v>380</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>21</v>
@@ -11300,26 +11330,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>21</v>
@@ -11328,15 +11358,17 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>480</v>
+        <v>382</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -11361,13 +11393,13 @@
         <v>21</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>280</v>
+        <v>21</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>482</v>
+        <v>21</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>483</v>
+        <v>21</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>21</v>
@@ -11385,22 +11417,22 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>479</v>
+        <v>385</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>85</v>
+        <v>380</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>21</v>
@@ -11414,42 +11446,46 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>327</v>
+        <v>132</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>485</v>
+        <v>449</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -11497,19 +11533,19 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>85</v>
@@ -11524,12 +11560,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11537,13 +11573,13 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>21</v>
@@ -11552,13 +11588,13 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>367</v>
+        <v>490</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>368</v>
+        <v>491</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11585,13 +11621,13 @@
         <v>21</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>21</v>
+        <v>492</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>21</v>
+        <v>493</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>21</v>
@@ -11609,10 +11645,10 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>369</v>
+        <v>489</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>87</v>
@@ -11621,10 +11657,10 @@
         <v>21</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>21</v>
@@ -11638,21 +11674,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>21</v>
@@ -11664,17 +11700,15 @@
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>132</v>
+        <v>337</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>372</v>
+        <v>495</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -11711,34 +11745,34 @@
         <v>21</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>375</v>
+        <v>494</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>21</v>
@@ -11752,10 +11786,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11766,7 +11800,7 @@
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>21</v>
@@ -11775,23 +11809,19 @@
         <v>21</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L87" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="M87" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>21</v>
       </c>
@@ -11839,22 +11869,22 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>21</v>
@@ -11868,21 +11898,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>21</v>
@@ -11891,23 +11921,21 @@
         <v>21</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>253</v>
+        <v>132</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>492</v>
+        <v>382</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>493</v>
+        <v>383</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>21</v>
       </c>
@@ -11943,34 +11971,34 @@
         <v>21</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>423</v>
+        <v>385</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>424</v>
+        <v>380</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>21</v>
@@ -11984,10 +12012,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11998,7 +12026,7 @@
         <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>21</v>
@@ -12007,19 +12035,23 @@
         <v>21</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>495</v>
+        <v>387</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>21</v>
       </c>
@@ -12067,13 +12099,13 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>494</v>
+        <v>392</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>21</v>
@@ -12082,7 +12114,7 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>85</v>
+        <v>393</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>21</v>
@@ -12096,10 +12128,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12119,19 +12151,23 @@
         <v>21</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>499</v>
+        <v>263</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
       </c>
@@ -12179,7 +12215,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>498</v>
+        <v>433</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12194,20 +12230,244 @@
         <v>99</v>
       </c>
       <c r="AK90" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK91" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="AL90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN90" t="s" s="2">
+      <c r="AL91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN90">
+  <autoFilter ref="A1:AN92">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12217,7 +12477,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI89">
+  <conditionalFormatting sqref="A2:AI91">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
